--- a/LEER/EjemploAparatos.xlsx
+++ b/LEER/EjemploAparatos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Archivos AJM\Chamba\Nexen\ExcelLaravel\LEER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCDE83D-81B8-471B-BB0E-B6D79D8BB535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F125FBE-96D0-4A30-9375-9A541F8DE4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
     <t>https://images.unsplash.com/photo-1585338107529-13afc5f02586?auto=format&amp;fit=crop&amp;w=900&amp;q=80</t>
   </si>
   <si>
-    <t>https://images.unsplash.com/photo-1657632843433-e6a8b7451ac6?fm=jpg&amp;q=60&amp;w=3000&amp;auto=format&amp;fit=crop&amp;ixlib=rb-4.1.0&amp;ixid=M3wxMjA3fDB8MHxzZWFyY2h8MXx8NGslMjB3YWxscGFwZXIlMjBjb2xvcmZ1bCUyMHdhbGxwYXBlcnxlbnwwfHwwfHx8MA%3D%3D</t>
+    <t>https://images.ctfassets.net/w5r1fvmogo3f/8Bi56x61EUGBmMFngPvSI/0e4b363d372c061d72ecd6b731c0edd9/arctis_nova_5_wl_black_pdp_img_mobile_hero.png?fm=webp&amp;q=90&amp;fit=scale&amp;w=1875</t>
   </si>
 </sst>
 </file>
